--- a/SCRIPTS/APPLICATIONS/LogS agrochemical.xlsx
+++ b/SCRIPTS/APPLICATIONS/LogS agrochemical.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://6f33fa7f78ea46e2aaca-my.sharepoint.com/personal/william_zamoraramirez_ucr_ac_cr/Documents/Backup/SOLUBILIDAD/SCRIPTS/APPLICATIONS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="377" documentId="8_{A0CFDA36-6E32-4120-814C-D99704465575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE21DE33-7F5B-466B-A24D-7903060D1701}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="8_{A0CFDA36-6E32-4120-814C-D99704465575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21C5E881-C913-40CD-9BC0-73E52B694074}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{DCEA933E-B760-4621-BEA6-3F5BAC6D0DCA}"/>
   </bookViews>
@@ -610,9 +610,6 @@
     <t>Use GSE</t>
   </si>
   <si>
-    <t>dev</t>
-  </si>
-  <si>
     <t>Chewing Pest Insecticides</t>
   </si>
   <si>
@@ -623,6 +620,9 @@
   </si>
   <si>
     <t>Post-Emergency Herbicides</t>
+  </si>
+  <si>
+    <t>DlogS</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1050,7 @@
         <v>181</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>182</v>
@@ -1091,15 +1091,15 @@
         <f>ROUND(0.5-0.01*(F2-25)-E2,2)</f>
         <v>-5.31</v>
       </c>
-      <c r="J2" s="1" t="str">
-        <f>IF(ABS(H2-I2)&lt;=1,"NO","YES")</f>
-        <v>NO</v>
+      <c r="J2" s="1">
+        <f>ABS(H2-I2)</f>
+        <v>0.34999999999999964</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1133,15 +1133,15 @@
         <f t="shared" ref="I3:I66" si="2">ROUND(0.5-0.01*(F3-25)-E3,2)</f>
         <v>-4.0999999999999996</v>
       </c>
-      <c r="J3" s="1" t="str">
-        <f t="shared" ref="J3:J66" si="3">IF(ABS(H3-I3)&lt;=1,"NO","YES")</f>
-        <v>YES</v>
+      <c r="J3" s="1">
+        <f t="shared" ref="J3:J66" si="3">ABS(H3-I3)</f>
+        <v>1.1900000000000004</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1175,15 +1175,15 @@
         <f t="shared" si="2"/>
         <v>-3.81</v>
       </c>
-      <c r="J4" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J4" s="1">
+        <f t="shared" si="3"/>
+        <v>1.44</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1217,15 +1217,15 @@
         <f t="shared" si="2"/>
         <v>-7</v>
       </c>
-      <c r="J5" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J5" s="1">
+        <f t="shared" si="3"/>
+        <v>1.5300000000000002</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1260,15 +1260,15 @@
         <f t="shared" si="2"/>
         <v>-5.69</v>
       </c>
-      <c r="J6" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J6" s="1">
+        <f t="shared" si="3"/>
+        <v>2.1900000000000004</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1303,15 +1303,15 @@
         <f t="shared" si="2"/>
         <v>-3.86</v>
       </c>
-      <c r="J7" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J7" s="1">
+        <f t="shared" si="3"/>
+        <v>1.02</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1345,15 +1345,15 @@
         <f t="shared" si="2"/>
         <v>-5.28</v>
       </c>
-      <c r="J8" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J8" s="1">
+        <f t="shared" si="3"/>
+        <v>0.10999999999999943</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1388,15 +1388,15 @@
         <f t="shared" si="2"/>
         <v>-5.64</v>
       </c>
-      <c r="J9" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J9" s="1">
+        <f t="shared" si="3"/>
+        <v>0.19000000000000039</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1431,15 +1431,15 @@
         <f t="shared" si="2"/>
         <v>-4.96</v>
       </c>
-      <c r="J10" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J10" s="1">
+        <f t="shared" si="3"/>
+        <v>0.42999999999999972</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1473,15 +1473,15 @@
         <f t="shared" si="2"/>
         <v>-4.78</v>
       </c>
-      <c r="J11" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J11" s="1">
+        <f t="shared" si="3"/>
+        <v>0.66000000000000014</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1516,15 +1516,15 @@
         <f t="shared" si="2"/>
         <v>-6.06</v>
       </c>
-      <c r="J12" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J12" s="1">
+        <f t="shared" si="3"/>
+        <v>0.64999999999999947</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1558,15 +1558,15 @@
         <f t="shared" si="2"/>
         <v>-5.92</v>
       </c>
-      <c r="J13" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J13" s="1">
+        <f t="shared" si="3"/>
+        <v>0.51999999999999957</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1601,15 +1601,15 @@
         <f t="shared" si="2"/>
         <v>-5.0199999999999996</v>
       </c>
-      <c r="J14" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J14" s="1">
+        <f t="shared" si="3"/>
+        <v>7.9999999999999183E-2</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1644,15 +1644,15 @@
         <f t="shared" si="2"/>
         <v>-5.33</v>
       </c>
-      <c r="J15" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J15" s="1">
+        <f t="shared" si="3"/>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1686,15 +1686,15 @@
         <f t="shared" si="2"/>
         <v>-5.75</v>
       </c>
-      <c r="J16" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J16" s="1">
+        <f t="shared" si="3"/>
+        <v>0.33000000000000007</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1728,15 +1728,15 @@
         <f t="shared" si="2"/>
         <v>-4.78</v>
       </c>
-      <c r="J17" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J17" s="1">
+        <f t="shared" si="3"/>
+        <v>0.79</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1771,15 +1771,15 @@
         <f t="shared" si="2"/>
         <v>-4.17</v>
       </c>
-      <c r="J18" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J18" s="1">
+        <f t="shared" si="3"/>
+        <v>1.4000000000000004</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1813,15 +1813,15 @@
         <f t="shared" si="2"/>
         <v>-5.41</v>
       </c>
-      <c r="J19" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J19" s="1">
+        <f t="shared" si="3"/>
+        <v>0.54999999999999982</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1856,15 +1856,15 @@
         <f t="shared" si="2"/>
         <v>-4.83</v>
       </c>
-      <c r="J20" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J20" s="1">
+        <f t="shared" si="3"/>
+        <v>0.38999999999999968</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1898,15 +1898,15 @@
         <f t="shared" si="2"/>
         <v>-5.74</v>
       </c>
-      <c r="J21" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J21" s="1">
+        <f t="shared" si="3"/>
+        <v>0.45999999999999996</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1941,15 +1941,15 @@
         <f t="shared" si="2"/>
         <v>-5.74</v>
       </c>
-      <c r="J22" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J22" s="1">
+        <f t="shared" si="3"/>
+        <v>1.46</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1983,15 +1983,15 @@
         <f t="shared" si="2"/>
         <v>-1.04</v>
       </c>
-      <c r="J23" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J23" s="1">
+        <f t="shared" si="3"/>
+        <v>1.3399999999999999</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -2025,15 +2025,15 @@
         <f t="shared" si="2"/>
         <v>-1.72</v>
       </c>
-      <c r="J24" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J24" s="1">
+        <f t="shared" si="3"/>
+        <v>1.3299999999999998</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -2067,15 +2067,15 @@
         <f t="shared" si="2"/>
         <v>-3.43</v>
       </c>
-      <c r="J25" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J25" s="1">
+        <f t="shared" si="3"/>
+        <v>0.46999999999999975</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2109,15 +2109,15 @@
         <f t="shared" si="2"/>
         <v>0.22</v>
       </c>
-      <c r="J26" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J26" s="1">
+        <f t="shared" si="3"/>
+        <v>2.6100000000000003</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2151,15 +2151,15 @@
         <f t="shared" si="2"/>
         <v>-1.1200000000000001</v>
       </c>
-      <c r="J27" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J27" s="1">
+        <f t="shared" si="3"/>
+        <v>1.2199999999999998</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2193,15 +2193,15 @@
         <f t="shared" si="2"/>
         <v>-1.26</v>
       </c>
-      <c r="J28" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J28" s="1">
+        <f t="shared" si="3"/>
+        <v>1.8099999999999998</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -2235,15 +2235,15 @@
         <f t="shared" si="2"/>
         <v>0.59</v>
       </c>
-      <c r="J29" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J29" s="1">
+        <f t="shared" si="3"/>
+        <v>2.9699999999999998</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2277,15 +2277,15 @@
         <f t="shared" si="2"/>
         <v>-1.24</v>
       </c>
-      <c r="J30" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J30" s="1">
+        <f t="shared" si="3"/>
+        <v>1.76</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2320,15 +2320,15 @@
         <f t="shared" si="2"/>
         <v>-3.76</v>
       </c>
-      <c r="J31" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J31" s="1">
+        <f t="shared" si="3"/>
+        <v>1.4300000000000006</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2362,15 +2362,15 @@
         <f t="shared" si="2"/>
         <v>-3.18</v>
       </c>
-      <c r="J32" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J32" s="1">
+        <f t="shared" si="3"/>
+        <v>0.7799999999999998</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2404,15 +2404,15 @@
         <f t="shared" si="2"/>
         <v>-1.18</v>
       </c>
-      <c r="J33" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J33" s="1">
+        <f t="shared" si="3"/>
+        <v>1.6199999999999999</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2446,15 +2446,15 @@
         <f t="shared" si="2"/>
         <v>-1.34</v>
       </c>
-      <c r="J34" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J34" s="1">
+        <f t="shared" si="3"/>
+        <v>1.7899999999999998</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2488,15 +2488,15 @@
         <f t="shared" si="2"/>
         <v>-0.51</v>
       </c>
-      <c r="J35" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J35" s="1">
+        <f t="shared" si="3"/>
+        <v>2.5700000000000003</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2530,15 +2530,15 @@
         <f t="shared" si="2"/>
         <v>-3.68</v>
       </c>
-      <c r="J36" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J36" s="1">
+        <f t="shared" si="3"/>
+        <v>0.44999999999999973</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2572,15 +2572,15 @@
         <f t="shared" si="2"/>
         <v>-2.91</v>
       </c>
-      <c r="J37" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J37" s="1">
+        <f t="shared" si="3"/>
+        <v>1.8499999999999996</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2614,15 +2614,15 @@
         <f t="shared" si="2"/>
         <v>-5.03</v>
       </c>
-      <c r="J38" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J38" s="1">
+        <f t="shared" si="3"/>
+        <v>0.52999999999999936</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2656,15 +2656,15 @@
         <f t="shared" si="2"/>
         <v>-3.98</v>
       </c>
-      <c r="J39" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J39" s="1">
+        <f t="shared" si="3"/>
+        <v>1.3599999999999999</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2699,15 +2699,15 @@
         <f t="shared" si="2"/>
         <v>-3.65</v>
       </c>
-      <c r="J40" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J40" s="1">
+        <f t="shared" si="3"/>
+        <v>1.2600000000000002</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2742,15 +2742,15 @@
         <f t="shared" si="2"/>
         <v>-3.81</v>
       </c>
-      <c r="J41" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J41" s="1">
+        <f t="shared" si="3"/>
+        <v>0.69999999999999973</v>
       </c>
       <c r="K41" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2785,15 +2785,15 @@
         <f t="shared" si="2"/>
         <v>-2.4700000000000002</v>
       </c>
-      <c r="J42" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J42" s="1">
+        <f t="shared" si="3"/>
+        <v>0.60999999999999988</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2827,15 +2827,15 @@
         <f t="shared" si="2"/>
         <v>-3.41</v>
       </c>
-      <c r="J43" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J43" s="1">
+        <f t="shared" si="3"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2869,15 +2869,15 @@
         <f t="shared" si="2"/>
         <v>-4.01</v>
       </c>
-      <c r="J44" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J44" s="1">
+        <f t="shared" si="3"/>
+        <v>0.47000000000000064</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2912,15 +2912,15 @@
         <f t="shared" si="2"/>
         <v>-3.95</v>
       </c>
-      <c r="J45" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J45" s="1">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2955,15 +2955,15 @@
         <f t="shared" si="2"/>
         <v>-3.75</v>
       </c>
-      <c r="J46" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J46" s="1">
+        <f t="shared" si="3"/>
+        <v>1.0099999999999998</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2997,15 +2997,15 @@
         <f t="shared" si="2"/>
         <v>-3.28</v>
       </c>
-      <c r="J47" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J47" s="1">
+        <f t="shared" si="3"/>
+        <v>1.0500000000000003</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -3040,15 +3040,15 @@
         <f t="shared" si="2"/>
         <v>-3.17</v>
       </c>
-      <c r="J48" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J48" s="1">
+        <f t="shared" si="3"/>
+        <v>2.17</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -3083,15 +3083,15 @@
         <f t="shared" si="2"/>
         <v>-4.4400000000000004</v>
       </c>
-      <c r="J49" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J49" s="1">
+        <f t="shared" si="3"/>
+        <v>0.85999999999999943</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -3126,15 +3126,15 @@
         <f t="shared" si="2"/>
         <v>-3.48</v>
       </c>
-      <c r="J50" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J50" s="1">
+        <f t="shared" si="3"/>
+        <v>1.1999999999999997</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -3168,15 +3168,15 @@
         <f t="shared" si="2"/>
         <v>-3.9</v>
       </c>
-      <c r="J51" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J51" s="1">
+        <f t="shared" si="3"/>
+        <v>1.0900000000000003</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -3210,15 +3210,15 @@
         <f t="shared" si="2"/>
         <v>-3.59</v>
       </c>
-      <c r="J52" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J52" s="1">
+        <f t="shared" si="3"/>
+        <v>0.46999999999999975</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -3253,15 +3253,15 @@
         <f t="shared" si="2"/>
         <v>-5.0599999999999996</v>
       </c>
-      <c r="J53" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J53" s="1">
+        <f t="shared" si="3"/>
+        <v>0.17000000000000082</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -3295,15 +3295,15 @@
         <f t="shared" si="2"/>
         <v>-3.66</v>
       </c>
-      <c r="J54" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J54" s="1">
+        <f t="shared" si="3"/>
+        <v>0.88999999999999968</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -3337,15 +3337,15 @@
         <f t="shared" si="2"/>
         <v>-3.6</v>
       </c>
-      <c r="J55" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J55" s="1">
+        <f t="shared" si="3"/>
+        <v>1.6400000000000001</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -3380,15 +3380,15 @@
         <f t="shared" si="2"/>
         <v>-3.26</v>
       </c>
-      <c r="J56" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J56" s="1">
+        <f t="shared" si="3"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -3422,15 +3422,15 @@
         <f t="shared" si="2"/>
         <v>-2.74</v>
       </c>
-      <c r="J57" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J57" s="1">
+        <f t="shared" si="3"/>
+        <v>0.1599999999999997</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -3465,15 +3465,15 @@
         <f t="shared" si="2"/>
         <v>-4.49</v>
       </c>
-      <c r="J58" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J58" s="1">
+        <f t="shared" si="3"/>
+        <v>0.79</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3507,15 +3507,15 @@
         <f t="shared" si="2"/>
         <v>-3.76</v>
       </c>
-      <c r="J59" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J59" s="1">
+        <f t="shared" si="3"/>
+        <v>0.78000000000000025</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3549,15 +3549,15 @@
         <f t="shared" si="2"/>
         <v>-4</v>
       </c>
-      <c r="J60" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J60" s="1">
+        <f t="shared" si="3"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3591,15 +3591,15 @@
         <f t="shared" si="2"/>
         <v>-2.34</v>
       </c>
-      <c r="J61" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J61" s="1">
+        <f t="shared" si="3"/>
+        <v>1.7400000000000002</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3633,15 +3633,15 @@
         <f t="shared" si="2"/>
         <v>-4.4800000000000004</v>
       </c>
-      <c r="J62" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>NO</v>
+      <c r="J62" s="1">
+        <f t="shared" si="3"/>
+        <v>0.87999999999999989</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3675,15 +3675,15 @@
         <f t="shared" si="2"/>
         <v>-0.83</v>
       </c>
-      <c r="J63" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J63" s="1">
+        <f t="shared" si="3"/>
+        <v>1.69</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3717,15 +3717,15 @@
         <f t="shared" si="2"/>
         <v>1.98</v>
       </c>
-      <c r="J64" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J64" s="1">
+        <f t="shared" si="3"/>
+        <v>4.3100000000000005</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3760,15 +3760,15 @@
         <f t="shared" si="2"/>
         <v>-0.46</v>
       </c>
-      <c r="J65" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J65" s="1">
+        <f t="shared" si="3"/>
+        <v>3.18</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3803,15 +3803,15 @@
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
-      <c r="J66" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>YES</v>
+      <c r="J66" s="1">
+        <f t="shared" si="3"/>
+        <v>2.41</v>
       </c>
       <c r="K66" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3846,15 +3846,15 @@
         <f t="shared" ref="I67:I87" si="6">ROUND(0.5-0.01*(F67-25)-E67,2)</f>
         <v>1.48</v>
       </c>
-      <c r="J67" s="1" t="str">
-        <f t="shared" ref="J67:J87" si="7">IF(ABS(H67-I67)&lt;=1,"NO","YES")</f>
-        <v>YES</v>
+      <c r="J67" s="1">
+        <f t="shared" ref="J67:J87" si="7">ABS(H67-I67)</f>
+        <v>3.81</v>
       </c>
       <c r="K67" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3889,15 +3889,15 @@
         <f t="shared" si="6"/>
         <v>-0.34</v>
       </c>
-      <c r="J68" s="1" t="str">
+      <c r="J68" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>2.27</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3932,15 +3932,15 @@
         <f t="shared" si="6"/>
         <v>-4.88</v>
       </c>
-      <c r="J69" s="1" t="str">
+      <c r="J69" s="1">
         <f t="shared" si="7"/>
-        <v>NO</v>
+        <v>0.67999999999999972</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3975,15 +3975,15 @@
         <f t="shared" si="6"/>
         <v>-0.1</v>
       </c>
-      <c r="J70" s="1" t="str">
+      <c r="J70" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>3.32</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -4017,15 +4017,15 @@
         <f t="shared" si="6"/>
         <v>-4.47</v>
       </c>
-      <c r="J71" s="1" t="str">
+      <c r="J71" s="1">
         <f t="shared" si="7"/>
-        <v>NO</v>
+        <v>0.58999999999999986</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -4060,15 +4060,15 @@
         <f t="shared" si="6"/>
         <v>-1.64</v>
       </c>
-      <c r="J72" s="1" t="str">
+      <c r="J72" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>1.28</v>
       </c>
       <c r="K72" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -4102,15 +4102,15 @@
         <f t="shared" si="6"/>
         <v>-0.72</v>
       </c>
-      <c r="J73" s="1" t="str">
+      <c r="J73" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>3.24</v>
       </c>
       <c r="K73" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -4144,15 +4144,15 @@
         <f t="shared" si="6"/>
         <v>0.1</v>
       </c>
-      <c r="J74" s="1" t="str">
+      <c r="J74" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="K74" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -4187,15 +4187,15 @@
         <f t="shared" si="6"/>
         <v>-3.66</v>
       </c>
-      <c r="J75" s="1" t="str">
+      <c r="J75" s="1">
         <f t="shared" si="7"/>
-        <v>NO</v>
+        <v>0.36000000000000032</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -4229,15 +4229,15 @@
         <f t="shared" si="6"/>
         <v>0.1</v>
       </c>
-      <c r="J76" s="1" t="str">
+      <c r="J76" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>3.13</v>
       </c>
       <c r="K76" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -4271,15 +4271,15 @@
         <f t="shared" si="6"/>
         <v>-0.32</v>
       </c>
-      <c r="J77" s="1" t="str">
+      <c r="J77" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>3.1300000000000003</v>
       </c>
       <c r="K77" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -4313,15 +4313,15 @@
         <f t="shared" si="6"/>
         <v>-1.25</v>
       </c>
-      <c r="J78" s="1" t="str">
+      <c r="J78" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>1.73</v>
       </c>
       <c r="K78" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -4355,15 +4355,15 @@
         <f t="shared" si="6"/>
         <v>0.67</v>
       </c>
-      <c r="J79" s="1" t="str">
+      <c r="J79" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>3.87</v>
       </c>
       <c r="K79" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -4397,15 +4397,15 @@
         <f t="shared" si="6"/>
         <v>-2.41</v>
       </c>
-      <c r="J80" s="1" t="str">
+      <c r="J80" s="1">
         <f t="shared" si="7"/>
-        <v>NO</v>
+        <v>0.96</v>
       </c>
       <c r="K80" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -4439,15 +4439,15 @@
         <f t="shared" si="6"/>
         <v>-1.45</v>
       </c>
-      <c r="J81" s="1" t="str">
+      <c r="J81" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>1.82</v>
       </c>
       <c r="K81" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -4481,15 +4481,15 @@
         <f t="shared" si="6"/>
         <v>-3.51</v>
       </c>
-      <c r="J82" s="1" t="str">
+      <c r="J82" s="1">
         <f t="shared" si="7"/>
-        <v>NO</v>
+        <v>0.32000000000000028</v>
       </c>
       <c r="K82" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -4523,15 +4523,15 @@
         <f t="shared" si="6"/>
         <v>-0.17</v>
       </c>
-      <c r="J83" s="1" t="str">
+      <c r="J83" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>2.31</v>
       </c>
       <c r="K83" s="1" t="s">
         <v>183</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -4566,15 +4566,15 @@
         <f t="shared" si="6"/>
         <v>-2.2400000000000002</v>
       </c>
-      <c r="J84" s="1" t="str">
+      <c r="J84" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>1.0199999999999996</v>
       </c>
       <c r="K84" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4608,15 +4608,15 @@
         <f t="shared" si="6"/>
         <v>-2.39</v>
       </c>
-      <c r="J85" s="1" t="str">
+      <c r="J85" s="1">
         <f t="shared" si="7"/>
-        <v>YES</v>
+        <v>1.7799999999999998</v>
       </c>
       <c r="K85" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4650,15 +4650,15 @@
         <f t="shared" si="6"/>
         <v>-5.04</v>
       </c>
-      <c r="J86" s="1" t="str">
+      <c r="J86" s="1">
         <f t="shared" si="7"/>
-        <v>NO</v>
+        <v>0.25</v>
       </c>
       <c r="K86" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4692,15 +4692,15 @@
         <f t="shared" si="6"/>
         <v>-2.11</v>
       </c>
-      <c r="J87" s="1" t="str">
+      <c r="J87" s="1">
         <f t="shared" si="7"/>
-        <v>NO</v>
+        <v>0.78000000000000025</v>
       </c>
       <c r="K87" s="1" t="s">
         <v>184</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
